--- a/Stats Sheet/Round Gaps/To The End.xlsx
+++ b/Stats Sheet/Round Gaps/To The End.xlsx
@@ -586,10 +586,10 @@
     <x:t>IsaacMT</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
-  </x:si>
-  <x:si>
     <x:t>LimitDTW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>TorinFBF</x:t>
@@ -4276,12 +4276,9 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="D98" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC98" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="AD98" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
@@ -4296,9 +4293,12 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="D99" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AC99" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="AD99" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
